--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T1_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>63</t>
+    <t>57</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.524</t>
-  </si>
-  <si>
-    <t>(0.063)</t>
-  </si>
-  <si>
-    <t>0.333</t>
-  </si>
-  <si>
-    <t>(0.060)</t>
-  </si>
-  <si>
-    <t>1.190</t>
-  </si>
-  <si>
-    <t>(0.211)</t>
-  </si>
-  <si>
-    <t>0.444</t>
-  </si>
-  <si>
-    <t>(0.093)</t>
+    <t>0.579</t>
+  </si>
+  <si>
+    <t>(0.066)</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>1.316</t>
+  </si>
+  <si>
+    <t>(0.227)</t>
+  </si>
+  <si>
+    <t>0.491</t>
+  </si>
+  <si>
+    <t>(0.101)</t>
   </si>
   <si>
     <t>53</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.363***</t>
-  </si>
-  <si>
-    <t>0.289***</t>
-  </si>
-  <si>
-    <t>3.206***</t>
-  </si>
-  <si>
-    <t>1.178***</t>
+    <t>0.308***</t>
+  </si>
+  <si>
+    <t>0.254***</t>
+  </si>
+  <si>
+    <t>3.080***</t>
+  </si>
+  <si>
+    <t>1.131***</t>
   </si>
 </sst>
 </file>
